--- a/Endereços Transitorios.xlsx
+++ b/Endereços Transitorios.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.alves\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Armazem\103\05 - ACURACIDADE\01 - INTERNO\103\08 - INDICADORES\ENDEREÇOS TRANSITORIOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A71A77-D6C9-4C5D-8351-B86E5EB7B68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2286E293-C57C-47B4-930A-A22F2C64018D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{07F0759F-BA98-45D1-B5D3-80B0D1902D00}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{07F0759F-BA98-45D1-B5D3-80B0D1902D00}"/>
   </bookViews>
   <sheets>
     <sheet name="Endereços Transitórios" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Endereços Transitórios'!$A$1:$B$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Endereços Transitórios'!$A$1:$B$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="52">
   <si>
     <t>AJUSTEDEESTOQUE</t>
   </si>
@@ -179,55 +179,25 @@
     <t>RESPONSAVEL</t>
   </si>
   <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>TEMPO DE ROTA</t>
-  </si>
-  <si>
-    <t>0H</t>
-  </si>
-  <si>
-    <t>CLAUDIO</t>
-  </si>
-  <si>
-    <t>JEFFERSON</t>
-  </si>
-  <si>
-    <t>PAVÃO</t>
-  </si>
-  <si>
-    <t>UILSON</t>
-  </si>
-  <si>
-    <t>72H</t>
-  </si>
-  <si>
     <t>SHEILA</t>
   </si>
   <si>
-    <t>SPRIAVARIAEC02</t>
-  </si>
-  <si>
-    <t>SPRIAVARIAEC04</t>
-  </si>
-  <si>
-    <t>VANESSA / LUCAS FERNANDO / ANDRW</t>
-  </si>
-  <si>
-    <t>168H</t>
-  </si>
-  <si>
-    <t>INDEFINIDO</t>
-  </si>
-  <si>
-    <t>24H</t>
-  </si>
-  <si>
-    <t>AGNALDO / JEFERSON / PAVÃO</t>
-  </si>
-  <si>
-    <t>MIRIAN ( INVENTARIO )</t>
+    <t>TEMPO DE ROTA (dia)</t>
+  </si>
+  <si>
+    <t>ACURACIDADE</t>
+  </si>
+  <si>
+    <t>SUCESSO DO CLIENTE</t>
+  </si>
+  <si>
+    <t>WAGNER / JOÃO / ANDREW</t>
+  </si>
+  <si>
+    <t>UILSON / EWYLYN / EDSON</t>
+  </si>
+  <si>
+    <t>CLAUDIO / EWYLYN</t>
   </si>
 </sst>
 </file>
@@ -269,13 +239,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -283,14 +249,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -326,6 +284,14 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -340,16 +306,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3A919849-AF8D-4CE4-94DB-87AF51C08816}" name="Tabela1" displayName="Tabela1" ref="A1:D40" totalsRowShown="0" dataDxfId="0">
-  <autoFilter ref="A1:D40" xr:uid="{3A919849-AF8D-4CE4-94DB-87AF51C08816}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D40">
-    <sortCondition ref="C1:C40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3A919849-AF8D-4CE4-94DB-87AF51C08816}" name="Tabela1" displayName="Tabela1" ref="A1:D38" totalsRowShown="0" dataDxfId="4">
+  <autoFilter ref="A1:D38" xr:uid="{3A919849-AF8D-4CE4-94DB-87AF51C08816}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D38">
+    <sortCondition ref="A1:A38"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4D672D09-B24D-41D7-A658-1858D10B7581}" name="ENDEREÇO" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{E503B869-B769-443B-A4B3-08FBF4EF8836}" name="AZ" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{469CC39D-9879-4A27-B55E-3A899E0E1ED7}" name="RESPONSAVEL" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{A88560AE-49A4-4D86-933B-0C80ADAB0AB8}" name="TEMPO DE ROTA" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{4D672D09-B24D-41D7-A658-1858D10B7581}" name="ENDEREÇO" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{E503B869-B769-443B-A4B3-08FBF4EF8836}" name="AZ" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{469CC39D-9879-4A27-B55E-3A899E0E1ED7}" name="RESPONSAVEL" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{A88560AE-49A4-4D86-933B-0C80ADAB0AB8}" name="TEMPO DE ROTA (dia)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -672,13 +638,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8182271-F35F-4A19-94A4-DEFE680759C5}">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -696,549 +662,521 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="C7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="C8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B35" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B36" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="C36" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="C37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="1">
         <v>3</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C38" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>57</v>
+      <c r="D38" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
